--- a/Template/KWS9_SOW.xlsx
+++ b/Template/KWS9_SOW.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\msys2\home\sheyiqi\github\MD_Group\Template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MSYS2\home\yiqis\github\MD_Group\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98DD15ED-CEEF-4F1D-86EE-806BAB133C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32BD86DA-3940-4123-9D39-96DE102D8572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5640" yWindow="7200" windowWidth="20424" windowHeight="18504" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 2" sheetId="4" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="157">
   <si>
     <t>Table Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -390,10 +390,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2026/9/15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Table: 封装测试计划</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -410,14 +406,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>HTOL Testchip Report</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HTOL Test</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>T0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -443,10 +431,6 @@
   </si>
   <si>
     <t>T0 + 3.5 month</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>T0 + 7 month</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -498,10 +482,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1P9M(TBD)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>16k</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -550,22 +530,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2026/11/1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026/10/27</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026/10/23</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026/10/22</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2026/10/15</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -578,10 +542,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2026/9/21</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>D1240 HC6T</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -598,10 +558,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>VDDE(V)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Nominal</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -618,7 +574,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>VSSE(V)</t>
+    <t>1P8M(TBD)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026/11/25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026/11/15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026/8/25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026/10/10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026/11/30</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -924,12 +900,6 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -937,6 +907,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1229,13 +1205,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F98AF4D1-6549-4199-AC71-314A5ADE1460}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="42.88671875" customWidth="1"/>
-    <col min="2" max="2" width="10.77734375" customWidth="1"/>
+    <col min="1" max="1" width="42.875" customWidth="1"/>
+    <col min="2" max="2" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1243,36 +1219,36 @@
         <v>17</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -1284,14 +1260,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4EA2ECF-93A1-44B5-8689-5C67F3903905}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.109375" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" customWidth="1"/>
-    <col min="3" max="3" width="20.88671875" customWidth="1"/>
+    <col min="1" max="1" width="25.125" customWidth="1"/>
+    <col min="2" max="2" width="14.25" customWidth="1"/>
+    <col min="3" max="3" width="20.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -1299,45 +1275,45 @@
         <v>89</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A2" s="21" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A3" s="22"/>
       <c r="B3" s="15" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A4" s="22"/>
       <c r="B4" s="15" t="s">
         <v>90</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A5" s="23"/>
       <c r="B5" s="15" t="s">
         <v>91</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -1353,14 +1329,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAE41AAA-8C15-486A-A70D-82A4F7C63D41}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.21875" customWidth="1"/>
+    <col min="1" max="1" width="24.25" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
-    <col min="4" max="4" width="13.6640625" customWidth="1"/>
+    <col min="4" max="4" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1377,9 +1353,9 @@
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
-        <v>123</v>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="16" t="s">
+        <v>119</v>
       </c>
       <c r="B2" s="10">
         <v>1</v>
@@ -1394,8 +1370,8 @@
         <v>105</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="18"/>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="16"/>
       <c r="B3" s="10">
         <v>2</v>
       </c>
@@ -1409,8 +1385,8 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="18"/>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="16"/>
       <c r="B4" s="10">
         <v>3</v>
       </c>
@@ -1421,11 +1397,11 @@
         <v>107</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="16"/>
       <c r="B5" s="10">
         <v>4</v>
       </c>
@@ -1433,14 +1409,14 @@
         <v>95</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="16"/>
       <c r="B6" s="10">
         <v>5</v>
       </c>
@@ -1448,14 +1424,14 @@
         <v>96</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>108</v>
+        <v>155</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="18"/>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="16"/>
       <c r="B7" s="10">
         <v>6</v>
       </c>
@@ -1463,14 +1439,14 @@
         <v>97</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="18"/>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="16"/>
       <c r="B8" s="10">
         <v>7</v>
       </c>
@@ -1478,14 +1454,14 @@
         <v>98</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="18"/>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="16"/>
       <c r="B9" s="10">
         <v>8</v>
       </c>
@@ -1493,14 +1469,14 @@
         <v>99</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="18"/>
+        <v>152</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="16"/>
       <c r="B10" s="10">
         <v>9</v>
       </c>
@@ -1508,10 +1484,10 @@
         <v>100</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -1525,15 +1501,15 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C23F822-AF2A-438F-A3B4-81476D3D8CF2}">
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.21875" customWidth="1"/>
+    <col min="1" max="1" width="24.25" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
-    <col min="4" max="4" width="13.6640625" customWidth="1"/>
+    <col min="4" max="4" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1544,98 +1520,74 @@
         <v>101</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
-        <v>109</v>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="16" t="s">
+        <v>108</v>
       </c>
       <c r="B2" s="10">
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="18"/>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="16"/>
       <c r="B3" s="10">
         <v>2</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="18"/>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="16"/>
       <c r="B4" s="10">
         <v>3</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="16"/>
       <c r="B5" s="10">
         <v>4</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="16"/>
       <c r="B6" s="10">
         <v>5</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="18"/>
-      <c r="B7" s="10">
-        <v>6</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="18"/>
-      <c r="B8" s="10">
-        <v>7</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:A8"/>
+    <mergeCell ref="A2:A6"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1645,14 +1597,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40619ABD-E572-444F-B205-E6F0CD395CFA}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="35.21875" customWidth="1"/>
-    <col min="3" max="3" width="38.77734375" customWidth="1"/>
-    <col min="4" max="4" width="17.33203125" customWidth="1"/>
+    <col min="1" max="1" width="35.25" customWidth="1"/>
+    <col min="3" max="3" width="38.75" customWidth="1"/>
+    <col min="4" max="4" width="17.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1666,9 +1618,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
-        <v>126</v>
+    <row r="2" spans="1:4" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>15</v>
@@ -1677,11 +1629,11 @@
         <v>19</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="18"/>
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="16"/>
       <c r="B3" s="10" t="s">
         <v>16</v>
       </c>
@@ -1689,31 +1641,31 @@
         <v>18</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="18"/>
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="16"/>
       <c r="B4" s="10" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="16"/>
       <c r="B5" s="10" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>21</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -1728,14 +1680,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34A8DB4A-58BD-4BB4-A87C-0E0F736365FB}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="35.21875" customWidth="1"/>
-    <col min="3" max="3" width="38.77734375" customWidth="1"/>
-    <col min="4" max="4" width="17.33203125" customWidth="1"/>
+    <col min="1" max="1" width="35.25" customWidth="1"/>
+    <col min="3" max="3" width="38.75" customWidth="1"/>
+    <col min="4" max="4" width="17.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1749,8 +1701,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+    <row r="2" spans="1:4" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="17" t="s">
         <v>34</v>
       </c>
       <c r="B2" s="10" t="s">
@@ -1760,11 +1712,11 @@
         <v>19</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20"/>
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="18"/>
       <c r="B3" s="10" t="s">
         <v>16</v>
       </c>
@@ -1772,31 +1724,31 @@
         <v>18</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="20"/>
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="18"/>
       <c r="B4" s="10" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="20"/>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="18"/>
       <c r="B5" s="10" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>21</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -1811,13 +1763,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCC641E5-B08E-4BF9-AF39-3E9AD6AB7462}">
   <dimension ref="A1:J5"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="53.33203125" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="53.375" customWidth="1"/>
+    <col min="5" max="5" width="11.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1849,8 +1801,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" s="16" t="s">
         <v>22</v>
       </c>
       <c r="B2" s="2">
@@ -1881,8 +1833,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="18"/>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="16"/>
       <c r="B3" s="2">
         <v>2</v>
       </c>
@@ -1911,8 +1863,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="18"/>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" s="16"/>
       <c r="B4" s="2">
         <v>4</v>
       </c>
@@ -1941,8 +1893,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="16"/>
       <c r="B5" s="2">
         <v>4</v>
       </c>
@@ -1983,13 +1935,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51292F90-E6BB-47B7-8424-ED8217B2715E}">
   <dimension ref="A1:J5"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="53.33203125" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="53.375" customWidth="1"/>
+    <col min="5" max="5" width="11.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2021,8 +1973,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" s="16" t="s">
         <v>23</v>
       </c>
       <c r="B2" s="2">
@@ -2053,8 +2005,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="18"/>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="16"/>
       <c r="B3" s="2">
         <v>2</v>
       </c>
@@ -2062,7 +2014,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2">
         <v>32</v>
@@ -2083,8 +2035,8 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="18"/>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" s="16"/>
       <c r="B4" s="2">
         <v>4</v>
       </c>
@@ -2113,8 +2065,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="16"/>
       <c r="B5" s="2">
         <v>4</v>
       </c>
@@ -2122,7 +2074,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="2">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E5" s="2">
         <v>64</v>
@@ -2155,13 +2107,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B04511EA-F7FD-4F13-BC7F-6696711F80D1}">
   <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="53.33203125" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="53.375" customWidth="1"/>
+    <col min="5" max="5" width="11.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2193,8 +2145,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" s="19" t="s">
         <v>24</v>
       </c>
       <c r="B2" s="2">
@@ -2222,11 +2174,11 @@
         <v>256</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="20"/>
       <c r="B3" s="2">
         <v>2</v>
       </c>
@@ -2252,11 +2204,11 @@
         <v>256</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="17"/>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" s="20"/>
       <c r="B4" s="2">
         <v>2</v>
       </c>
@@ -2282,11 +2234,11 @@
         <v>256</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="17"/>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="20"/>
       <c r="B5" s="2">
         <v>2</v>
       </c>
@@ -2315,8 +2267,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" s="20"/>
       <c r="B6" s="2">
         <v>4</v>
       </c>
@@ -2342,11 +2294,11 @@
         <v>128</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="17"/>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="20"/>
       <c r="B7" s="2">
         <v>4</v>
       </c>
@@ -2372,11 +2324,11 @@
         <v>128</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="17"/>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="20"/>
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -2402,11 +2354,11 @@
         <v>128</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="17"/>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="20"/>
       <c r="B9" s="2">
         <v>4</v>
       </c>
@@ -2447,13 +2399,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB24599-813B-4A17-9A91-43B0216E65F3}">
   <dimension ref="A1:J13"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="63" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2485,8 +2437,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" s="19" t="s">
         <v>25</v>
       </c>
       <c r="B2" s="2">
@@ -2517,8 +2469,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="20"/>
       <c r="B3" s="2">
         <v>4</v>
       </c>
@@ -2547,8 +2499,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="17"/>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" s="20"/>
       <c r="B4" s="2">
         <v>4</v>
       </c>
@@ -2577,8 +2529,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="17"/>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="20"/>
       <c r="B5" s="2">
         <v>4</v>
       </c>
@@ -2607,8 +2559,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" s="20"/>
       <c r="B6" s="2">
         <v>8</v>
       </c>
@@ -2637,8 +2589,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="17"/>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="20"/>
       <c r="B7" s="2">
         <v>8</v>
       </c>
@@ -2667,8 +2619,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="17"/>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="20"/>
       <c r="B8" s="2">
         <v>8</v>
       </c>
@@ -2697,8 +2649,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="17"/>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="20"/>
       <c r="B9" s="2">
         <v>8</v>
       </c>
@@ -2727,8 +2679,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="17"/>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" s="20"/>
       <c r="B10" s="2">
         <v>16</v>
       </c>
@@ -2757,8 +2709,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="17"/>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" s="20"/>
       <c r="B11" s="2">
         <v>16</v>
       </c>
@@ -2787,8 +2739,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="17"/>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" s="20"/>
       <c r="B12" s="2">
         <v>16</v>
       </c>
@@ -2817,8 +2769,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="17"/>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" s="20"/>
       <c r="B13" s="2">
         <v>16</v>
       </c>
@@ -2858,16 +2810,16 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F23BCBF9-16F4-4CFD-946E-F8D5918F6152}">
-  <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="64.33203125" customWidth="1"/>
+    <col min="1" max="1" width="64.375" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="5" max="7" width="11.21875" customWidth="1"/>
-    <col min="9" max="9" width="25.33203125" customWidth="1"/>
+    <col min="5" max="5" width="11.25" customWidth="1"/>
+    <col min="7" max="7" width="25.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2884,20 +2836,14 @@
         <v>38</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>157</v>
+        <v>39</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="I1" s="9" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="16" t="s">
         <v>88</v>
       </c>
       <c r="B2" s="10" t="s">
@@ -2913,20 +2859,14 @@
         <v>0.8</v>
       </c>
       <c r="F2" s="10">
-        <v>0</v>
-      </c>
-      <c r="G2" s="10">
-        <v>0</v>
-      </c>
-      <c r="H2" s="10">
         <v>25</v>
       </c>
-      <c r="I2" s="10" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="18"/>
+      <c r="G2" s="10" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="16"/>
       <c r="B3" s="10" t="s">
         <v>43</v>
       </c>
@@ -2940,20 +2880,14 @@
         <v>0.8</v>
       </c>
       <c r="F3" s="10">
-        <v>0</v>
-      </c>
-      <c r="G3" s="10">
-        <v>0</v>
-      </c>
-      <c r="H3" s="10">
         <v>85</v>
       </c>
-      <c r="I3" s="10" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="18"/>
+      <c r="G3" s="10" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="16"/>
       <c r="B4" s="10" t="s">
         <v>44</v>
       </c>
@@ -2967,20 +2901,14 @@
         <v>0.72</v>
       </c>
       <c r="F4" s="10">
-        <v>0</v>
-      </c>
-      <c r="G4" s="10">
-        <v>0</v>
-      </c>
-      <c r="H4" s="10">
         <v>-40</v>
       </c>
-      <c r="I4" s="10" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
+      <c r="G4" s="10" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="16"/>
       <c r="B5" s="10" t="s">
         <v>45</v>
       </c>
@@ -2994,20 +2922,14 @@
         <v>0.72</v>
       </c>
       <c r="F5" s="10">
-        <v>0</v>
-      </c>
-      <c r="G5" s="10">
-        <v>0</v>
-      </c>
-      <c r="H5" s="10">
         <v>125</v>
       </c>
-      <c r="I5" s="10" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
+      <c r="G5" s="10" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="16"/>
       <c r="B6" s="10" t="s">
         <v>44</v>
       </c>
@@ -3021,20 +2943,14 @@
         <v>0.72</v>
       </c>
       <c r="F6" s="10">
-        <v>0.7</v>
-      </c>
-      <c r="G6" s="10">
-        <v>-1.5</v>
-      </c>
-      <c r="H6" s="10">
         <v>-40</v>
       </c>
-      <c r="I6" s="10" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="18"/>
+      <c r="G6" s="10" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="16"/>
       <c r="B7" s="10" t="s">
         <v>45</v>
       </c>
@@ -3048,22 +2964,16 @@
         <v>0.72</v>
       </c>
       <c r="F7" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="G7" s="10">
-        <v>-1</v>
-      </c>
-      <c r="H7" s="10">
         <v>125</v>
       </c>
-      <c r="I7" s="10" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="18"/>
+      <c r="G7" s="10" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="16"/>
       <c r="B8" s="10" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>40</v>
@@ -3075,22 +2985,16 @@
         <v>0.8</v>
       </c>
       <c r="F8" s="10">
-        <v>0</v>
-      </c>
-      <c r="G8" s="10">
-        <v>0</v>
-      </c>
-      <c r="H8" s="10">
         <v>25</v>
       </c>
-      <c r="I8" s="10" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="18"/>
+      <c r="G8" s="10" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="16"/>
       <c r="B9" s="10" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>40</v>
@@ -3102,16 +3006,10 @@
         <v>0.8</v>
       </c>
       <c r="F9" s="10">
-        <v>0</v>
-      </c>
-      <c r="G9" s="10">
-        <v>0</v>
-      </c>
-      <c r="H9" s="10">
         <v>85</v>
       </c>
-      <c r="I9" s="10" t="s">
-        <v>158</v>
+      <c r="G9" s="10" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -3126,14 +3024,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{708EFA42-0B00-4065-B708-67F0DF91E50F}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="52.6640625" customWidth="1"/>
-    <col min="2" max="2" width="39.77734375" customWidth="1"/>
-    <col min="3" max="3" width="76.33203125" customWidth="1"/>
+    <col min="1" max="1" width="52.625" customWidth="1"/>
+    <col min="2" max="2" width="39.75" customWidth="1"/>
+    <col min="3" max="3" width="76.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3144,8 +3042,8 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="17" t="s">
         <v>86</v>
       </c>
       <c r="B2" s="7" t="s">
@@ -3155,8 +3053,8 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="20"/>
+    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="18"/>
       <c r="B3" s="7" t="s">
         <v>50</v>
       </c>
@@ -3164,8 +3062,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="20"/>
+    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="18"/>
       <c r="B4" s="7" t="s">
         <v>52</v>
       </c>
@@ -3173,8 +3071,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="20"/>
+    <row r="5" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="18"/>
       <c r="B5" s="7" t="s">
         <v>54</v>
       </c>
@@ -3182,8 +3080,8 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="20"/>
+    <row r="6" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="18"/>
       <c r="B6" s="7" t="s">
         <v>56</v>
       </c>
@@ -3191,8 +3089,8 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="20"/>
+    <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="18"/>
       <c r="B7" s="7" t="s">
         <v>58</v>
       </c>
@@ -3200,8 +3098,8 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="20"/>
+    <row r="8" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="18"/>
       <c r="B8" s="7" t="s">
         <v>60</v>
       </c>
@@ -3209,8 +3107,8 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="20"/>
+    <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="18"/>
       <c r="B9" s="7" t="s">
         <v>62</v>
       </c>
@@ -3218,8 +3116,8 @@
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="20"/>
+    <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="18"/>
       <c r="B10" s="7" t="s">
         <v>64</v>
       </c>
@@ -3227,8 +3125,8 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="20"/>
+    <row r="11" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="18"/>
       <c r="B11" s="7" t="s">
         <v>66</v>
       </c>
@@ -3236,8 +3134,8 @@
         <v>67</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="20"/>
+    <row r="12" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="18"/>
       <c r="B12" s="7" t="s">
         <v>68</v>
       </c>
@@ -3245,8 +3143,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="20"/>
+    <row r="13" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="18"/>
       <c r="B13" s="7" t="s">
         <v>70</v>
       </c>
@@ -3254,8 +3152,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="20"/>
+    <row r="14" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="18"/>
       <c r="B14" s="7" t="s">
         <v>72</v>
       </c>
@@ -3263,8 +3161,8 @@
         <v>73</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="20"/>
+    <row r="15" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="18"/>
       <c r="B15" s="7" t="s">
         <v>74</v>
       </c>
@@ -3272,8 +3170,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="20"/>
+    <row r="16" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="18"/>
       <c r="B16" s="7" t="s">
         <v>76</v>
       </c>
@@ -3281,8 +3179,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="20"/>
+    <row r="17" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="18"/>
       <c r="B17" s="7" t="s">
         <v>78</v>
       </c>
@@ -3290,8 +3188,8 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="20"/>
+    <row r="18" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="18"/>
       <c r="B18" s="7" t="s">
         <v>80</v>
       </c>
@@ -3299,8 +3197,8 @@
         <v>81</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="20"/>
+    <row r="19" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="18"/>
       <c r="B19" s="7" t="s">
         <v>82</v>
       </c>
@@ -3308,8 +3206,8 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="20"/>
+    <row r="20" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="18"/>
       <c r="B20" s="7" t="s">
         <v>84</v>
       </c>

--- a/Template/KWS9_SOW.xlsx
+++ b/Template/KWS9_SOW.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MSYS2\home\yiqis\github\MD_Group\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32BD86DA-3940-4123-9D39-96DE102D8572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38DC0B26-0C7A-4A43-9D1C-F26E6B7EE46B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 2" sheetId="4" r:id="rId1"/>
@@ -25,6 +25,9 @@
     <sheet name="Table 7" sheetId="15" r:id="rId10"/>
     <sheet name="Table 8" sheetId="16" r:id="rId11"/>
     <sheet name="Table 9" sheetId="17" r:id="rId12"/>
+    <sheet name="Table 10" sheetId="19" r:id="rId13"/>
+    <sheet name="Table 11" sheetId="20" r:id="rId14"/>
+    <sheet name="Table 12" sheetId="21" r:id="rId15"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="177">
   <si>
     <t>Table Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -390,10 +393,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Table: 封装测试计划</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Testchip Package</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -431,10 +430,6 @@
   </si>
   <si>
     <t>T0 + 3.5 month</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Table: 测试片开发计划</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -455,8 +450,146 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>PDK Version</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Metal Stack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TFBGA(TBD)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16k</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>32k</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>64k</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.110</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.124</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.185</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.274</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8T2P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KWS9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GF22nm(TBD)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~5mm*5mm(TBD)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026/10/15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026/8/15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026/8/22</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D1240 HC6T</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D1850 8T2P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nominal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FuncCmax</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TT0P65V0P8V25CTT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TT0P65V0P8V85CTT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1P8M(TBD)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026/11/25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026/11/15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026/8/25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026/10/10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026/11/30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Table: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>第一阶段</t>
     </r>
     <r>
       <rPr>
@@ -470,131 +603,112 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>PDK Version</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Metal Stack</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TFBGA(TBD)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>16k</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>32k</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>64k</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.110</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.124</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.185</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.274</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8T2P</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>KWS9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GF22nm(TBD)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>~5mm*5mm(TBD)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026/10/15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026/8/15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026/8/22</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>D1240 HC6T</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>D1850 8T2P</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>P3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>P4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Nominal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FuncCmax</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TT0P65V0P8V25CTT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TT0P65V0P8V85CTT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1P8M(TBD)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026/11/25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026/11/15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026/8/25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026/10/10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026/11/30</t>
+    <t>Table: 第一阶段测试片开发计划</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Table: 第一阶段封装测试计划</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Table: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>第二阶段</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+      </rPr>
+      <t>测试片信息</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KWS11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Table: 第二阶段测试片开发计划</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Table: 第二阶段封装测试计划</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026/12/01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026/12/05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2027/3/15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2027/3/20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026/12/1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2027/1/31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2027/1/15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2027/2/15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026/12/20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026/12/15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2027/3/1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2027/6/25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2027/6/15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2027/6/1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2027/6/30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SOI 22nm(TBD)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -602,7 +716,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -668,6 +782,13 @@
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="1"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1219,16 +1340,16 @@
         <v>17</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1236,19 +1357,19 @@
         <v>33</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C2" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="F2" s="13" t="s">
         <v>131</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -1275,27 +1396,27 @@
         <v>89</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A2" s="21" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A3" s="22"/>
       <c r="B3" s="15" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
@@ -1304,7 +1425,7 @@
         <v>90</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
@@ -1313,7 +1434,7 @@
         <v>91</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -1355,7 +1476,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
-        <v>119</v>
+        <v>155</v>
       </c>
       <c r="B2" s="10">
         <v>1</v>
@@ -1397,7 +1518,7 @@
         <v>107</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -1409,10 +1530,10 @@
         <v>95</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -1424,10 +1545,10 @@
         <v>96</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -1439,10 +1560,10 @@
         <v>97</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -1454,10 +1575,10 @@
         <v>98</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -1469,10 +1590,10 @@
         <v>99</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -1484,10 +1605,10 @@
         <v>100</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -1520,21 +1641,21 @@
         <v>101</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
-        <v>108</v>
+        <v>156</v>
       </c>
       <c r="B2" s="10">
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -1543,10 +1664,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -1555,10 +1676,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="D4" s="13" t="s">
         <v>116</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -1567,10 +1688,10 @@
         <v>4</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -1579,10 +1700,347 @@
         <v>5</v>
       </c>
       <c r="C6" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>117</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A6"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E2A6B2C-A44A-4428-A072-3E207A8A5358}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="25.125" customWidth="1"/>
+    <col min="2" max="2" width="14.25" customWidth="1"/>
+    <col min="3" max="3" width="20.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="22"/>
+      <c r="B3" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="22"/>
+      <c r="B4" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="23"/>
+      <c r="B5" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>136</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A5"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93CFDE81-AA5C-4CAA-9A39-B64FFD0E7B6C}">
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="24.25" customWidth="1"/>
+    <col min="3" max="3" width="27" customWidth="1"/>
+    <col min="4" max="4" width="13.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="B2" s="10">
+        <v>1</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="16"/>
+      <c r="B3" s="10">
+        <v>2</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="16"/>
+      <c r="B4" s="10">
+        <v>3</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="16"/>
+      <c r="B5" s="10">
+        <v>4</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="16"/>
+      <c r="B6" s="10">
+        <v>5</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="16"/>
+      <c r="B7" s="10">
+        <v>6</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="16"/>
+      <c r="B8" s="10">
+        <v>7</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="16"/>
+      <c r="B9" s="10">
+        <v>8</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="16"/>
+      <c r="B10" s="10">
+        <v>9</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>175</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A10"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0461EA20-6944-4893-8643-E20B1C2A3F0E}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="24.25" customWidth="1"/>
+    <col min="3" max="3" width="27" customWidth="1"/>
+    <col min="4" max="4" width="13.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="B2" s="10">
+        <v>1</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D2" s="13" t="s">
         <v>111</v>
       </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="16"/>
+      <c r="B3" s="10">
+        <v>2</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="16"/>
+      <c r="B4" s="10">
+        <v>3</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="16"/>
+      <c r="B5" s="10">
+        <v>4</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="16"/>
+      <c r="B6" s="10">
+        <v>5</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>110</v>
+      </c>
       <c r="D6" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -1620,7 +2078,7 @@
     </row>
     <row r="2" spans="1:4" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>15</v>
@@ -1629,7 +2087,7 @@
         <v>19</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1641,31 +2099,31 @@
         <v>18</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="16"/>
       <c r="B4" s="10" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="16"/>
       <c r="B5" s="10" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>21</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -1712,7 +2170,7 @@
         <v>19</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1724,31 +2182,31 @@
         <v>18</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="18"/>
       <c r="B4" s="10" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="18"/>
       <c r="B5" s="10" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>21</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -2174,7 +2632,7 @@
         <v>256</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -2204,7 +2662,7 @@
         <v>256</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -2234,7 +2692,7 @@
         <v>256</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -2294,7 +2752,7 @@
         <v>128</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -2324,7 +2782,7 @@
         <v>128</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -2354,7 +2812,7 @@
         <v>128</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -2862,7 +3320,7 @@
         <v>25</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -2883,7 +3341,7 @@
         <v>85</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -2904,7 +3362,7 @@
         <v>-40</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -2925,7 +3383,7 @@
         <v>125</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -2946,7 +3404,7 @@
         <v>-40</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -2967,13 +3425,13 @@
         <v>125</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="16"/>
       <c r="B8" s="10" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>40</v>
@@ -2988,13 +3446,13 @@
         <v>25</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="16"/>
       <c r="B9" s="10" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>40</v>
@@ -3009,7 +3467,7 @@
         <v>85</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/Template/KWS9_SOW.xlsx
+++ b/Template/KWS9_SOW.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MSYS2\home\yiqis\github\MD_Group\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38DC0B26-0C7A-4A43-9D1C-F26E6B7EE46B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4BA0B45-2C0E-4B14-A30E-A54F93D0F883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="178">
   <si>
     <t>Table Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -117,10 +117,6 @@
   </si>
   <si>
     <t>Ultra High Density Single Port SRAM Compiler</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Table: Ultra High Density Two Port Register File 容量范围定义</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -709,6 +705,14 @@
   </si>
   <si>
     <t>SOI 22nm(TBD)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>High Density Pseudo Two Port Register File</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Table: High Density Pseudo Two Port Register File 容量范围定义</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1340,36 +1344,36 @@
         <v>17</v>
       </c>
       <c r="C1" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="D1" s="9" t="s">
-        <v>119</v>
-      </c>
       <c r="E1" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>132</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C2" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="D2" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="E2" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="F2" s="13" t="s">
         <v>130</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -1393,48 +1397,48 @@
         <v>0</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A2" s="21" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A3" s="22"/>
       <c r="B3" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A4" s="22"/>
       <c r="B4" s="15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A5" s="23"/>
       <c r="B5" s="15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -1462,33 +1466,33 @@
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="D1" s="12" t="s">
+      <c r="E1" s="12" t="s">
         <v>103</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B2" s="10">
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -1497,13 +1501,13 @@
         <v>2</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -1512,13 +1516,13 @@
         <v>3</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -1527,13 +1531,13 @@
         <v>4</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -1542,13 +1546,13 @@
         <v>5</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -1557,13 +1561,13 @@
         <v>6</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -1572,13 +1576,13 @@
         <v>7</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -1587,13 +1591,13 @@
         <v>8</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -1602,13 +1606,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -1635,27 +1639,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B2" s="10">
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -1664,10 +1668,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -1676,10 +1680,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" s="13" t="s">
         <v>115</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -1688,10 +1692,10 @@
         <v>4</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -1700,10 +1704,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -1730,48 +1734,48 @@
         <v>0</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A2" s="21" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A3" s="22"/>
       <c r="B3" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A4" s="22"/>
       <c r="B4" s="15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A5" s="23"/>
       <c r="B5" s="15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -1799,33 +1803,33 @@
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="D1" s="12" t="s">
+      <c r="E1" s="12" t="s">
         <v>103</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B2" s="10">
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -1834,13 +1838,13 @@
         <v>2</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -1849,13 +1853,13 @@
         <v>3</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -1864,13 +1868,13 @@
         <v>4</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D5" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="E5" s="13" t="s">
         <v>167</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -1879,13 +1883,13 @@
         <v>5</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D6" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="E6" s="13" t="s">
         <v>163</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -1894,13 +1898,13 @@
         <v>6</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -1909,13 +1913,13 @@
         <v>7</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -1924,13 +1928,13 @@
         <v>8</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -1939,13 +1943,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -1972,27 +1976,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B2" s="10">
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -2001,10 +2005,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -2013,10 +2017,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" s="13" t="s">
         <v>115</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -2025,10 +2029,10 @@
         <v>4</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -2037,10 +2041,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -2078,7 +2082,7 @@
     </row>
     <row r="2" spans="1:4" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>15</v>
@@ -2087,7 +2091,7 @@
         <v>19</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2099,31 +2103,31 @@
         <v>18</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="16"/>
       <c r="B4" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="16"/>
       <c r="B5" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>21</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -2161,7 +2165,7 @@
     </row>
     <row r="2" spans="1:4" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>15</v>
@@ -2170,7 +2174,7 @@
         <v>19</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2179,34 +2183,34 @@
         <v>16</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>18</v>
+        <v>176</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="18"/>
       <c r="B4" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="18"/>
       <c r="B5" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>21</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -2261,7 +2265,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
-        <v>22</v>
+        <v>177</v>
       </c>
       <c r="B2" s="2">
         <v>2</v>
@@ -2433,7 +2437,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2">
         <v>2</v>
@@ -2460,7 +2464,7 @@
         <v>288</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -2490,7 +2494,7 @@
         <v>288</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -2520,7 +2524,7 @@
         <v>144</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -2550,7 +2554,7 @@
         <v>144</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -2605,7 +2609,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" s="2">
         <v>2</v>
@@ -2632,7 +2636,7 @@
         <v>256</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -2662,7 +2666,7 @@
         <v>256</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -2692,7 +2696,7 @@
         <v>256</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -2722,7 +2726,7 @@
         <v>256</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -2752,7 +2756,7 @@
         <v>128</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -2782,7 +2786,7 @@
         <v>128</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -2812,7 +2816,7 @@
         <v>128</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -2842,7 +2846,7 @@
         <v>128</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -2897,7 +2901,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" s="2">
         <v>4</v>
@@ -2924,7 +2928,7 @@
         <v>320</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -2954,7 +2958,7 @@
         <v>320</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -2984,7 +2988,7 @@
         <v>320</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -3014,7 +3018,7 @@
         <v>320</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -3044,7 +3048,7 @@
         <v>160</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -3074,7 +3078,7 @@
         <v>160</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -3104,7 +3108,7 @@
         <v>160</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -3134,7 +3138,7 @@
         <v>160</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -3164,7 +3168,7 @@
         <v>80</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
@@ -3194,7 +3198,7 @@
         <v>80</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -3224,7 +3228,7 @@
         <v>80</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
@@ -3254,7 +3258,7 @@
         <v>80</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -3282,33 +3286,33 @@
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="9" t="s">
-        <v>39</v>
-      </c>
       <c r="G1" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2" s="10">
         <v>0.8</v>
@@ -3320,16 +3324,16 @@
         <v>25</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="16"/>
       <c r="B3" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D3" s="10">
         <v>0.8</v>
@@ -3341,16 +3345,16 @@
         <v>85</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="16"/>
       <c r="B4" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D4" s="10">
         <v>0.72</v>
@@ -3362,16 +3366,16 @@
         <v>-40</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="16"/>
       <c r="B5" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5" s="10">
         <v>0.72</v>
@@ -3383,16 +3387,16 @@
         <v>125</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="16"/>
       <c r="B6" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D6" s="10">
         <v>0.72</v>
@@ -3404,16 +3408,16 @@
         <v>-40</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="16"/>
       <c r="B7" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D7" s="10">
         <v>0.72</v>
@@ -3425,16 +3429,16 @@
         <v>125</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="16"/>
       <c r="B8" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D8" s="10">
         <v>0.65</v>
@@ -3446,16 +3450,16 @@
         <v>25</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="16"/>
       <c r="B9" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D9" s="10">
         <v>0.65</v>
@@ -3467,7 +3471,7 @@
         <v>85</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -3494,183 +3498,183 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>48</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18"/>
       <c r="B3" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>50</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="18"/>
       <c r="B4" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>52</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="18"/>
       <c r="B5" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>54</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18"/>
       <c r="B6" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>56</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="18"/>
       <c r="B7" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>58</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="18"/>
       <c r="B8" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>60</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="18"/>
       <c r="B9" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>62</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="18"/>
       <c r="B10" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>64</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="18"/>
       <c r="B11" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>66</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="18"/>
       <c r="B12" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>68</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18"/>
       <c r="B13" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>70</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="18"/>
       <c r="B14" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>72</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18"/>
       <c r="B15" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>74</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="18"/>
       <c r="B16" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>76</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="18"/>
       <c r="B17" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>78</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="18"/>
       <c r="B18" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>80</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="18"/>
       <c r="B19" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>82</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="18"/>
       <c r="B20" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>84</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>85</v>
       </c>
     </row>
   </sheetData>
